--- a/Design-Files/LSS_Sub_Board_v1.1/BOM/Client_BOM-LSS_Sub_Board_v1.1.xlsx
+++ b/Design-Files/LSS_Sub_Board_v1.1/BOM/Client_BOM-LSS_Sub_Board_v1.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XPENDER\Documents\GitHub\ColeBenson-SmartMotors\Design-Files\LSS_Sub_Board_v1.1\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\ColeBenson-SmartMotors\Design-Files\LSS_Sub_Board_v1.1\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,31 +14,16 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
-  <si>
-    <t>Component list</t>
-  </si>
-  <si>
-    <t>Source Data From:</t>
-  </si>
-  <si>
-    <t>Project:</t>
-  </si>
-  <si>
-    <t>Variant:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Item Type</t>
   </si>
   <si>
@@ -99,23 +84,14 @@
     <t>-</t>
   </si>
   <si>
-    <t>Bill of Materials for Project [SM_Sub_Board_v1.1.]</t>
-  </si>
-  <si>
-    <t>SM_Sub_Board_v1.1.</t>
-  </si>
-  <si>
-    <t>Flexible Cable for J1</t>
+    <t>JST Cable for J1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-  </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -126,58 +102,6 @@
     <font>
       <sz val="10"/>
       <color indexed="13"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -197,29 +121,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -273,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -314,82 +215,7 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -457,174 +283,87 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -913,11 +652,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.140625" style="21" customWidth="1"/>
-    <col min="3" max="3" width="18" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="18" style="7" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.85546875" customWidth="1"/>
     <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
@@ -929,247 +668,147 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
-    <row r="2" spans="1:10" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="24"/>
+      <c r="B2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="D2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="39"/>
+        <v>4</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="41" t="s">
+      <c r="B3" s="12">
+        <f>ROW(B3) - ROW($B$2)</f>
         <v>1</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44"/>
+      <c r="C3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="10">
+        <v>532610371</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="10">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="17"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="41" t="s">
+      <c r="B4" s="13">
+        <f t="shared" ref="B4" si="0">ROW(B4) - ROW($B$2)</f>
         <v>2</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="45"/>
+      <c r="C4" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="14">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="41" t="s">
+      <c r="B5" s="17">
         <v>3</v>
       </c>
-      <c r="E5" s="41"/>
-      <c r="F5" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="45"/>
+      <c r="C5" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="45"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="23"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="47"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="51"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="47"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="48"/>
-      <c r="J8" s="49"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="29">
-        <f>ROW(B10) - ROW($B$9)</f>
-        <v>1</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="27">
-        <v>532610371</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J10" s="27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="30">
-        <f t="shared" ref="B11" si="0">ROW(B11) - ROW($B$9)</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="J11" s="31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="37">
-        <v>3</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="31"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="54"/>
-      <c r="E13" s="55"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="57"/>
-      <c r="J13" s="58"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="59"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">
